--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -749,7 +749,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>23.96</v>
+        <v>23.62</v>
       </c>
       <c r="D2">
-        <v>-1.56</v>
+        <v>-1.42</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-52.17</v>
+        <v>-52.84</v>
       </c>
       <c r="H2">
-        <v>17.68</v>
+        <v>16.01</v>
       </c>
       <c r="I2">
-        <v>0.38</v>
+        <v>-1.87</v>
       </c>
       <c r="J2">
-        <v>-4.62</v>
+        <v>-5.44</v>
       </c>
       <c r="K2">
-        <v>-12.23</v>
+        <v>-13.48</v>
       </c>
       <c r="L2">
-        <v>-49.64</v>
+        <v>-47.74</v>
       </c>
       <c r="M2">
-        <v>14.64</v>
+        <v>15.38</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>5</v>
       </c>
       <c r="P2">
-        <v>24.16</v>
+        <v>24.07</v>
       </c>
       <c r="Q2">
-        <v>24.02</v>
+        <v>23.97</v>
       </c>
       <c r="R2">
-        <v>25.3</v>
+        <v>25.23</v>
       </c>
       <c r="S2">
-        <v>29.72</v>
+        <v>29.62</v>
       </c>
       <c r="T2">
-        <v>-19.39</v>
+        <v>-20.26</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>44.37</v>
+        <v>40.86</v>
       </c>
       <c r="Z2">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="AA2">
-        <v>-0.47</v>
+        <v>-0.45</v>
       </c>
       <c r="AB2">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="AC2">
-        <v>90.01000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="AD2">
-        <v>96.67</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="AE2">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AF2">
-        <v>-3.83</v>
+        <v>-18.28</v>
       </c>
       <c r="AG2">
-        <v>24.81</v>
+        <v>24.75</v>
       </c>
       <c r="AH2">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AI2">
         <v>25.79</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>26.5</v>
+        <v>24.76</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.82</v>
+        <v>-4.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.62</v>
+        <v>-5.44</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.8</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>3.97</v>
+        <v>0.38</v>
       </c>
       <c r="D8" s="5">
-        <v>0.38</v>
+        <v>-1.87</v>
       </c>
       <c r="E8" s="6">
-        <v>-3.59</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-51.41</v>
+        <v>-49.64</v>
       </c>
       <c r="D9" s="5">
-        <v>-49.64</v>
+        <v>-47.74</v>
       </c>
       <c r="E9" s="7">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.04</v>
+        <v>-12.23</v>
       </c>
       <c r="D10" s="5">
-        <v>-12.23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.8100000000000001</v>
+        <v>-13.48</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-51.41</v>
+        <v>-52.17</v>
       </c>
       <c r="D11" s="5">
-        <v>-52.17</v>
+        <v>-52.84</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.76</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>24.34</v>
+        <v>23.96</v>
       </c>
       <c r="D12" s="5">
-        <v>23.96</v>
+        <v>23.62</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.38</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>48.73</v>
+        <v>44.37</v>
       </c>
       <c r="D13" s="5">
-        <v>44.37</v>
+        <v>40.86</v>
       </c>
       <c r="E13" s="6">
-        <v>-4.36</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>169.81</v>
+        <v>-3.83</v>
       </c>
       <c r="D14" s="5">
-        <v>-3.83</v>
+        <v>-18.28</v>
       </c>
       <c r="E14" s="6">
-        <v>-173.64</v>
+        <v>-14.45</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>44.4</v>
+        <v>40.9</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.6</v>
+        <v>-5.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-12.2</v>
+        <v>-13.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1464</v>
+        <v>0.1538</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>23.62</v>
+        <v>23.38</v>
       </c>
       <c r="D2">
-        <v>-1.42</v>
+        <v>-1.02</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-52.84</v>
+        <v>-53.32</v>
       </c>
       <c r="H2">
-        <v>16.01</v>
+        <v>14.83</v>
       </c>
       <c r="I2">
-        <v>-1.87</v>
+        <v>-3.27</v>
       </c>
       <c r="J2">
-        <v>-5.44</v>
+        <v>-4.65</v>
       </c>
       <c r="K2">
-        <v>-13.48</v>
+        <v>-16.08</v>
       </c>
       <c r="L2">
-        <v>-47.74</v>
+        <v>-50.74</v>
       </c>
       <c r="M2">
-        <v>15.38</v>
+        <v>14.37</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>24.07</v>
+        <v>23.91</v>
       </c>
       <c r="Q2">
-        <v>23.97</v>
+        <v>23.92</v>
       </c>
       <c r="R2">
-        <v>25.23</v>
+        <v>25.16</v>
       </c>
       <c r="S2">
-        <v>29.62</v>
+        <v>29.51</v>
       </c>
       <c r="T2">
-        <v>-20.26</v>
+        <v>-20.78</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.86</v>
+        <v>38.53</v>
       </c>
       <c r="Z2">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="AA2">
-        <v>-0.45</v>
+        <v>-0.43</v>
       </c>
       <c r="AB2">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AC2">
-        <v>71.95</v>
+        <v>44.4</v>
       </c>
       <c r="AD2">
-        <v>87.31999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="AE2">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AF2">
-        <v>-18.28</v>
+        <v>-21.44</v>
       </c>
       <c r="AG2">
-        <v>24.75</v>
+        <v>24.73</v>
       </c>
       <c r="AH2">
-        <v>23.19</v>
+        <v>23.12</v>
       </c>
       <c r="AI2">
-        <v>25.79</v>
+        <v>25.75</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>24.76</v>
+        <v>21.59</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.62</v>
+        <v>-5.44</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.44</v>
+        <v>-4.65</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.82</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>0.38</v>
+        <v>-1.87</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.87</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.25</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-49.64</v>
+        <v>-47.74</v>
       </c>
       <c r="D9" s="5">
-        <v>-47.74</v>
+        <v>-50.74</v>
       </c>
       <c r="E9" s="7">
-        <v>1.9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-12.23</v>
+        <v>-13.48</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.48</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.25</v>
+        <v>-16.08</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-52.17</v>
+        <v>-52.84</v>
       </c>
       <c r="D11" s="5">
-        <v>-52.84</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.67</v>
+        <v>-53.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>23.96</v>
+        <v>23.62</v>
       </c>
       <c r="D12" s="5">
-        <v>23.62</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.34</v>
+        <v>23.38</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>44.37</v>
+        <v>40.86</v>
       </c>
       <c r="D13" s="5">
-        <v>40.86</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.51</v>
+        <v>38.53</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-3.83</v>
+        <v>-18.28</v>
       </c>
       <c r="D14" s="5">
-        <v>-18.28</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-14.45</v>
+        <v>-21.44</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.16</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>40.9</v>
+        <v>38.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.4</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-13.5</v>
+        <v>-16.1</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1538</v>
+        <v>0.1437</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -740,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>23.38</v>
+        <v>23.22</v>
       </c>
       <c r="D2">
-        <v>-1.02</v>
+        <v>-0.68</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,25 +886,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-53.32</v>
+        <v>-53.64</v>
       </c>
       <c r="H2">
-        <v>14.83</v>
+        <v>14.05</v>
       </c>
       <c r="I2">
-        <v>-3.27</v>
+        <v>-4.21</v>
       </c>
       <c r="J2">
-        <v>-4.65</v>
+        <v>-4.56</v>
       </c>
       <c r="K2">
-        <v>-16.08</v>
+        <v>-14.38</v>
       </c>
       <c r="L2">
-        <v>-50.74</v>
+        <v>-48.54</v>
       </c>
       <c r="M2">
-        <v>14.37</v>
+        <v>14.99</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +913,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>23.91</v>
+        <v>23.7</v>
       </c>
       <c r="Q2">
-        <v>23.92</v>
+        <v>23.86</v>
       </c>
       <c r="R2">
-        <v>25.16</v>
+        <v>25.09</v>
       </c>
       <c r="S2">
-        <v>29.51</v>
+        <v>29.4</v>
       </c>
       <c r="T2">
-        <v>-20.78</v>
+        <v>-21.03</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +940,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.53</v>
+        <v>37.02</v>
       </c>
       <c r="Z2">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="AA2">
         <v>-0.43</v>
       </c>
       <c r="AB2">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>44.4</v>
+        <v>22.75</v>
       </c>
       <c r="AD2">
-        <v>68.78</v>
+        <v>46.36</v>
       </c>
       <c r="AE2">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-21.44</v>
+        <v>-40.98</v>
       </c>
       <c r="AG2">
-        <v>24.73</v>
+        <v>24.65</v>
       </c>
       <c r="AH2">
-        <v>23.12</v>
+        <v>23.06</v>
       </c>
       <c r="AI2">
-        <v>25.75</v>
+        <v>25.52</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.59</v>
+        <v>19.23</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.44</v>
+        <v>-4.65</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.65</v>
+        <v>-4.56</v>
       </c>
       <c r="E7" s="6">
-        <v>0.79</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.87</v>
+        <v>-3.27</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.27</v>
+        <v>-4.21</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.4</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-47.74</v>
+        <v>-50.74</v>
       </c>
       <c r="D9" s="5">
-        <v>-50.74</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3</v>
+        <v>-48.54</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.48</v>
+        <v>-16.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-16.08</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.6</v>
+        <v>-14.38</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-52.84</v>
+        <v>-53.32</v>
       </c>
       <c r="D11" s="5">
-        <v>-53.32</v>
+        <v>-53.64</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.48</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>23.62</v>
+        <v>23.38</v>
       </c>
       <c r="D12" s="5">
-        <v>23.38</v>
+        <v>23.22</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>40.86</v>
+        <v>38.53</v>
       </c>
       <c r="D13" s="5">
-        <v>38.53</v>
+        <v>37.02</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.33</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-18.28</v>
+        <v>-21.44</v>
       </c>
       <c r="D14" s="5">
-        <v>-21.44</v>
+        <v>-40.98</v>
       </c>
       <c r="E14" s="7">
-        <v>-3.16</v>
+        <v>-19.54</v>
       </c>
     </row>
   </sheetData>
@@ -1363,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>38.5</v>
+        <v>37</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
@@ -1372,7 +1373,7 @@
         <v>-4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-16.1</v>
+        <v>-14.4</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1437</v>
+        <v>0.1499</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>23.22</v>
+        <v>22.98</v>
       </c>
       <c r="D2">
-        <v>-0.68</v>
+        <v>-1.03</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -886,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-53.64</v>
+        <v>-54.12</v>
       </c>
       <c r="H2">
-        <v>14.05</v>
+        <v>12.87</v>
       </c>
       <c r="I2">
-        <v>-4.21</v>
+        <v>-5.59</v>
       </c>
       <c r="J2">
-        <v>-4.56</v>
+        <v>-6.55</v>
       </c>
       <c r="K2">
-        <v>-14.38</v>
+        <v>-13.93</v>
       </c>
       <c r="L2">
-        <v>-48.54</v>
+        <v>-46.6</v>
       </c>
       <c r="M2">
-        <v>14.99</v>
+        <v>15.9</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>23.7</v>
+        <v>23.43</v>
       </c>
       <c r="Q2">
-        <v>23.86</v>
+        <v>23.78</v>
       </c>
       <c r="R2">
-        <v>25.09</v>
+        <v>25</v>
       </c>
       <c r="S2">
-        <v>29.4</v>
+        <v>29.29</v>
       </c>
       <c r="T2">
-        <v>-21.03</v>
+        <v>-21.55</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.02</v>
+        <v>34.82</v>
       </c>
       <c r="Z2">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="AA2">
         <v>-0.43</v>
       </c>
       <c r="AB2">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="AC2">
-        <v>22.75</v>
+        <v>7.48</v>
       </c>
       <c r="AD2">
-        <v>46.36</v>
+        <v>24.87</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>-40.98</v>
+        <v>-36.31</v>
       </c>
       <c r="AG2">
-        <v>24.65</v>
+        <v>24.62</v>
       </c>
       <c r="AH2">
-        <v>23.06</v>
+        <v>22.94</v>
       </c>
       <c r="AI2">
-        <v>25.52</v>
+        <v>25.23</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>19.23</v>
+        <v>18.97</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.65</v>
+        <v>-4.56</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.56</v>
+        <v>-6.55</v>
       </c>
       <c r="E7" s="6">
-        <v>0.09</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.27</v>
+        <v>-4.21</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.21</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-50.74</v>
+        <v>-48.54</v>
       </c>
       <c r="D9" s="5">
-        <v>-48.54</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2.2</v>
+        <v>-46.6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-16.08</v>
+        <v>-14.38</v>
       </c>
       <c r="D10" s="5">
-        <v>-14.38</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.7</v>
+        <v>-13.93</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.32</v>
+        <v>-53.64</v>
       </c>
       <c r="D11" s="5">
-        <v>-53.64</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.32</v>
+        <v>-54.12</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>23.38</v>
+        <v>23.22</v>
       </c>
       <c r="D12" s="5">
-        <v>23.22</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.16</v>
+        <v>22.98</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>38.53</v>
+        <v>37.02</v>
       </c>
       <c r="D13" s="5">
-        <v>37.02</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.51</v>
+        <v>34.82</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-21.44</v>
+        <v>-40.98</v>
       </c>
       <c r="D14" s="5">
-        <v>-40.98</v>
+        <v>-36.31</v>
       </c>
       <c r="E14" s="7">
-        <v>-19.54</v>
+        <v>4.67</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>37</v>
+        <v>34.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.6</v>
+        <v>-6.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-14.4</v>
+        <v>-13.9</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1499</v>
+        <v>0.159</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.98</v>
+        <v>22.72</v>
       </c>
       <c r="D2">
-        <v>-1.03</v>
+        <v>-1.13</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.12</v>
+        <v>-54.64</v>
       </c>
       <c r="H2">
-        <v>12.87</v>
+        <v>11.59</v>
       </c>
       <c r="I2">
-        <v>-5.59</v>
+        <v>-5.18</v>
       </c>
       <c r="J2">
-        <v>-6.55</v>
+        <v>-7.04</v>
       </c>
       <c r="K2">
-        <v>-13.93</v>
+        <v>-16.19</v>
       </c>
       <c r="L2">
-        <v>-46.6</v>
+        <v>-48.15</v>
       </c>
       <c r="M2">
-        <v>15.9</v>
+        <v>16.81</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>23.43</v>
+        <v>23.18</v>
       </c>
       <c r="Q2">
-        <v>23.78</v>
+        <v>23.7</v>
       </c>
       <c r="R2">
-        <v>25</v>
+        <v>24.88</v>
       </c>
       <c r="S2">
-        <v>29.29</v>
+        <v>29.19</v>
       </c>
       <c r="T2">
-        <v>-21.55</v>
+        <v>-22.16</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.82</v>
+        <v>32.55</v>
       </c>
       <c r="Z2">
-        <v>-0.43</v>
+        <v>-0.47</v>
       </c>
       <c r="AA2">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="AB2">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>7.48</v>
+        <v>1.7</v>
       </c>
       <c r="AD2">
-        <v>24.87</v>
+        <v>10.64</v>
       </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-36.31</v>
+        <v>25.73</v>
       </c>
       <c r="AG2">
-        <v>24.62</v>
+        <v>24.63</v>
       </c>
       <c r="AH2">
-        <v>22.94</v>
+        <v>22.78</v>
       </c>
       <c r="AI2">
-        <v>25.23</v>
+        <v>24.83</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>18.97</v>
+        <v>21.46</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.56</v>
+        <v>-6.55</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.55</v>
+        <v>-7.04</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.99</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.21</v>
+        <v>-5.59</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.59</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.38</v>
+        <v>-5.18</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-48.54</v>
+        <v>-46.6</v>
       </c>
       <c r="D9" s="5">
-        <v>-46.6</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.94</v>
+        <v>-48.15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.38</v>
+        <v>-13.93</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.93</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.45</v>
+        <v>-16.19</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.64</v>
+        <v>-54.12</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.12</v>
+        <v>-54.64</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.48</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>23.22</v>
+        <v>22.98</v>
       </c>
       <c r="D12" s="5">
-        <v>22.98</v>
+        <v>22.72</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.02</v>
+        <v>34.82</v>
       </c>
       <c r="D13" s="5">
-        <v>34.82</v>
+        <v>32.55</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.2</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-40.98</v>
+        <v>-36.31</v>
       </c>
       <c r="D14" s="5">
-        <v>-36.31</v>
+        <v>25.73</v>
       </c>
       <c r="E14" s="7">
-        <v>4.67</v>
+        <v>62.04</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>34.8</v>
+        <v>32.6</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.6</v>
+        <v>-7</v>
       </c>
       <c r="G2" s="10">
-        <v>-13.9</v>
+        <v>-16.2</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.159</v>
+        <v>0.1681</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.72</v>
+        <v>22.45</v>
       </c>
       <c r="D2">
-        <v>-1.13</v>
+        <v>-1.19</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.64</v>
+        <v>-55.18</v>
       </c>
       <c r="H2">
-        <v>11.59</v>
+        <v>10.27</v>
       </c>
       <c r="I2">
-        <v>-5.18</v>
+        <v>-4.95</v>
       </c>
       <c r="J2">
-        <v>-7.04</v>
+        <v>-7.69</v>
       </c>
       <c r="K2">
-        <v>-16.19</v>
+        <v>-17.25</v>
       </c>
       <c r="L2">
-        <v>-48.15</v>
+        <v>-48.93</v>
       </c>
       <c r="M2">
-        <v>16.81</v>
+        <v>16.2</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>23.18</v>
+        <v>22.95</v>
       </c>
       <c r="Q2">
-        <v>23.7</v>
+        <v>23.61</v>
       </c>
       <c r="R2">
-        <v>24.88</v>
+        <v>24.78</v>
       </c>
       <c r="S2">
-        <v>29.19</v>
+        <v>29.07</v>
       </c>
       <c r="T2">
-        <v>-22.16</v>
+        <v>-22.77</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.55</v>
+        <v>30.35</v>
       </c>
       <c r="Z2">
-        <v>-0.47</v>
+        <v>-0.52</v>
       </c>
       <c r="AA2">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.64</v>
+        <v>3.06</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>25.73</v>
+        <v>-28.32</v>
       </c>
       <c r="AG2">
-        <v>24.63</v>
+        <v>24.65</v>
       </c>
       <c r="AH2">
-        <v>22.78</v>
+        <v>22.57</v>
       </c>
       <c r="AI2">
-        <v>24.83</v>
+        <v>24.59</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.46</v>
+        <v>23.61</v>
       </c>
     </row>
   </sheetData>
@@ -1176,10 +1176,10 @@
         <v>-6.55</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.04</v>
+        <v>-7.69</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.49</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1193,10 +1193,10 @@
         <v>-5.59</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.18</v>
+        <v>-4.95</v>
       </c>
       <c r="E8" s="7">
-        <v>0.41</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1210,10 +1210,10 @@
         <v>-46.6</v>
       </c>
       <c r="D9" s="5">
-        <v>-48.15</v>
+        <v>-48.93</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.55</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1227,10 +1227,10 @@
         <v>-13.93</v>
       </c>
       <c r="D10" s="5">
-        <v>-16.19</v>
+        <v>-17.25</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.26</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1244,10 +1244,10 @@
         <v>-54.12</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.64</v>
+        <v>-55.18</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.52</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1261,10 +1261,10 @@
         <v>22.98</v>
       </c>
       <c r="D12" s="5">
-        <v>22.72</v>
+        <v>22.45</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.26</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1278,10 +1278,10 @@
         <v>34.82</v>
       </c>
       <c r="D13" s="5">
-        <v>32.55</v>
+        <v>30.35</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.27</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1295,10 +1295,10 @@
         <v>-36.31</v>
       </c>
       <c r="D14" s="5">
-        <v>25.73</v>
+        <v>-28.32</v>
       </c>
       <c r="E14" s="7">
-        <v>62.04</v>
+        <v>7.99</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>32.6</v>
+        <v>30.4</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-7</v>
+        <v>-7.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-16.2</v>
+        <v>-17.2</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1681</v>
+        <v>0.162</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -721,7 +721,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.45</v>
+        <v>21.7</v>
       </c>
       <c r="D2">
-        <v>-1.19</v>
+        <v>-3.34</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.18</v>
+        <v>-56.68</v>
       </c>
       <c r="H2">
-        <v>10.27</v>
+        <v>6.58</v>
       </c>
       <c r="I2">
-        <v>-4.95</v>
+        <v>-7.19</v>
       </c>
       <c r="J2">
-        <v>-7.69</v>
+        <v>-10.7</v>
       </c>
       <c r="K2">
-        <v>-17.25</v>
+        <v>-20.4</v>
       </c>
       <c r="L2">
-        <v>-48.93</v>
+        <v>-48.69</v>
       </c>
       <c r="M2">
-        <v>16.2</v>
+        <v>16.54</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>22.95</v>
+        <v>22.61</v>
       </c>
       <c r="Q2">
-        <v>23.61</v>
+        <v>23.49</v>
       </c>
       <c r="R2">
-        <v>24.78</v>
+        <v>24.66</v>
       </c>
       <c r="S2">
-        <v>29.07</v>
+        <v>28.95</v>
       </c>
       <c r="T2">
-        <v>-22.77</v>
+        <v>-25.03</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>30.35</v>
+        <v>25.23</v>
       </c>
       <c r="Z2">
-        <v>-0.52</v>
+        <v>-0.61</v>
       </c>
       <c r="AA2">
-        <v>-0.45</v>
+        <v>-0.49</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.06</v>
+        <v>0.57</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-28.32</v>
+        <v>-1.41</v>
       </c>
       <c r="AG2">
-        <v>24.65</v>
+        <v>24.8</v>
       </c>
       <c r="AH2">
-        <v>22.57</v>
+        <v>22.18</v>
       </c>
       <c r="AI2">
-        <v>24.59</v>
+        <v>24.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>23.61</v>
+        <v>28.17</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.55</v>
+        <v>-7.69</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.69</v>
+        <v>-10.7</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.14</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.59</v>
+        <v>-4.95</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.95</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.64</v>
+        <v>-7.19</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-46.6</v>
+        <v>-48.93</v>
       </c>
       <c r="D9" s="5">
-        <v>-48.93</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-2.33</v>
+        <v>-48.69</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.93</v>
+        <v>-17.25</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.25</v>
+        <v>-20.4</v>
       </c>
       <c r="E10" s="6">
-        <v>-3.32</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.12</v>
+        <v>-55.18</v>
       </c>
       <c r="D11" s="5">
-        <v>-55.18</v>
+        <v>-56.68</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.98</v>
+        <v>22.45</v>
       </c>
       <c r="D12" s="5">
-        <v>22.45</v>
+        <v>21.7</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.53</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>34.82</v>
+        <v>30.35</v>
       </c>
       <c r="D13" s="5">
-        <v>30.35</v>
+        <v>25.23</v>
       </c>
       <c r="E13" s="6">
-        <v>-4.47</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-36.31</v>
+        <v>-28.32</v>
       </c>
       <c r="D14" s="5">
-        <v>-28.32</v>
+        <v>-1.41</v>
       </c>
       <c r="E14" s="7">
-        <v>7.99</v>
+        <v>26.91</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.7</v>
+        <v>-10.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-17.2</v>
+        <v>-20.4</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.162</v>
+        <v>0.1654</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,7 +148,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.2 → 32.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.2</t>
+  </si>
+  <si>
+    <t>32.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -234,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,14 +377,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -721,7 +749,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -873,10 +901,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.7</v>
+        <v>22.15</v>
       </c>
       <c r="D2">
-        <v>-3.34</v>
+        <v>2.07</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -885,25 +913,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-56.68</v>
+        <v>-55.78</v>
       </c>
       <c r="H2">
-        <v>6.58</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I2">
-        <v>-7.19</v>
+        <v>-4.61</v>
       </c>
       <c r="J2">
-        <v>-10.7</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="K2">
-        <v>-20.4</v>
+        <v>-18.21</v>
       </c>
       <c r="L2">
-        <v>-48.69</v>
+        <v>-48.85</v>
       </c>
       <c r="M2">
-        <v>16.54</v>
+        <v>17.01</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +940,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.61</v>
+        <v>22.4</v>
       </c>
       <c r="Q2">
-        <v>23.49</v>
+        <v>23.42</v>
       </c>
       <c r="R2">
-        <v>24.66</v>
+        <v>24.57</v>
       </c>
       <c r="S2">
-        <v>28.95</v>
+        <v>28.82</v>
       </c>
       <c r="T2">
-        <v>-25.03</v>
+        <v>-23.15</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +967,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.23</v>
+        <v>32.58</v>
       </c>
       <c r="Z2">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="AA2">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="AB2">
         <v>-0.13</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>10.42</v>
       </c>
       <c r="AD2">
-        <v>0.57</v>
+        <v>3.47</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-1.41</v>
+        <v>51.81</v>
       </c>
       <c r="AG2">
-        <v>24.8</v>
+        <v>24.86</v>
       </c>
       <c r="AH2">
-        <v>22.18</v>
+        <v>21.98</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -975,7 +1003,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>28.17</v>
+        <v>30.29</v>
       </c>
     </row>
   </sheetData>
@@ -1136,12 +1164,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1149,156 +1212,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>47</v>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.69</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-10.7</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.01</v>
+      <c r="D7" s="6">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.95</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-7.19</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.24</v>
+      <c r="D8" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>-48.93</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-48.69</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.24</v>
+      <c r="D9" s="6">
+        <v>-48.85</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
-        <v>-17.25</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-20.4</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.15</v>
+      <c r="D10" s="6">
+        <v>-18.21</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="5">
-        <v>-55.18</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-56.68</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.5</v>
+      <c r="D11" s="6">
+        <v>-55.78</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="5">
-        <v>22.45</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>21.7</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.75</v>
+      <c r="D12" s="6">
+        <v>22.15</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5">
-        <v>30.35</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>25.23</v>
       </c>
-      <c r="E13" s="6">
-        <v>-5.12</v>
+      <c r="D13" s="6">
+        <v>32.58</v>
+      </c>
+      <c r="E13" s="7">
+        <v>7.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="5">
-        <v>-28.32</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-1.41</v>
       </c>
+      <c r="D14" s="6">
+        <v>51.81</v>
+      </c>
       <c r="E14" s="7">
-        <v>26.91</v>
+        <v>53.22</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1387,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>55</v>
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>25.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-20.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-18.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1542,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.1654</v>
+      <c r="A2" s="14">
+        <v>0.1701</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -148,34 +148,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.2 → 32.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.2</t>
-  </si>
-  <si>
-    <t>32.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -227,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,20 +234,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,12 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,22 +337,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -401,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -768,7 +726,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -901,10 +860,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.15</v>
+        <v>23.09</v>
       </c>
       <c r="D2">
-        <v>2.07</v>
+        <v>-1.54</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -913,46 +872,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.78</v>
+        <v>-53.9</v>
       </c>
       <c r="H2">
-        <v>8.789999999999999</v>
+        <v>13.41</v>
       </c>
       <c r="I2">
-        <v>-4.61</v>
+        <v>1.63</v>
       </c>
       <c r="J2">
-        <v>-8.359999999999999</v>
+        <v>-4.03</v>
       </c>
       <c r="K2">
-        <v>-18.21</v>
+        <v>-13.49</v>
       </c>
       <c r="L2">
-        <v>-48.85</v>
+        <v>-49.19</v>
       </c>
       <c r="M2">
-        <v>17.01</v>
+        <v>18.1</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>22.4</v>
+        <v>22.57</v>
       </c>
       <c r="Q2">
-        <v>23.42</v>
+        <v>23.36</v>
       </c>
       <c r="R2">
-        <v>24.57</v>
+        <v>24.46</v>
       </c>
       <c r="S2">
-        <v>28.82</v>
+        <v>28.63</v>
       </c>
       <c r="T2">
-        <v>-23.15</v>
+        <v>-19.36</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -967,34 +926,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.58</v>
+        <v>45.2</v>
       </c>
       <c r="Z2">
-        <v>-0.64</v>
+        <v>-0.51</v>
       </c>
       <c r="AA2">
         <v>-0.52</v>
       </c>
       <c r="AB2">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>10.42</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="AD2">
-        <v>3.47</v>
+        <v>41.72</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="AF2">
-        <v>51.81</v>
+        <v>12.47</v>
       </c>
       <c r="AG2">
-        <v>24.86</v>
+        <v>24.76</v>
       </c>
       <c r="AH2">
-        <v>21.98</v>
+        <v>21.96</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -1003,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>30.29</v>
+        <v>24.27</v>
       </c>
     </row>
   </sheetData>
@@ -1164,47 +1123,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1212,156 +1136,156 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.7</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="E7" s="7">
-        <v>2.34</v>
+      <c r="C7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.03</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6">
-        <v>-7.19</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.58</v>
+      <c r="C8" s="5">
+        <v>2.05</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.63</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
-        <v>-48.69</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-48.85</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.16</v>
+      <c r="C9" s="5">
+        <v>-45.82</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-49.19</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-18.21</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.19</v>
+      <c r="C10" s="5">
+        <v>-12.27</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-13.49</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
-        <v>-56.68</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-55.78</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.9</v>
+      <c r="C11" s="5">
+        <v>-53.18</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-53.9</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6">
-        <v>21.7</v>
-      </c>
-      <c r="D12" s="6">
-        <v>22.15</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.45</v>
+      <c r="C12" s="5">
+        <v>23.45</v>
+      </c>
+      <c r="D12" s="5">
+        <v>23.09</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="6">
-        <v>25.23</v>
-      </c>
-      <c r="D13" s="6">
-        <v>32.58</v>
-      </c>
-      <c r="E13" s="7">
-        <v>7.35</v>
+      <c r="C13" s="5">
+        <v>48.35</v>
+      </c>
+      <c r="D13" s="5">
+        <v>45.2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.41</v>
-      </c>
-      <c r="D14" s="6">
-        <v>51.81</v>
-      </c>
-      <c r="E14" s="7">
-        <v>53.22</v>
+      <c r="C14" s="5">
+        <v>233.91</v>
+      </c>
+      <c r="D14" s="5">
+        <v>12.47</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-221.44</v>
       </c>
     </row>
   </sheetData>
@@ -1387,60 +1311,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>64</v>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="11">
-        <v>32.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="9">
+        <v>45.2</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-18.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="9">
+        <v>-4</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-13.5</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1542,13 +1466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="14">
-        <v>0.1701</v>
+      <c r="A2" s="12">
+        <v>0.181</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -707,7 +707,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -726,8 +726,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -860,10 +859,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>23.09</v>
+        <v>22.7</v>
       </c>
       <c r="D2">
-        <v>-1.54</v>
+        <v>-1.69</v>
       </c>
       <c r="E2">
         <v>50.09</v>
@@ -872,46 +871,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-53.9</v>
+        <v>-54.68</v>
       </c>
       <c r="H2">
-        <v>13.41</v>
+        <v>11.49</v>
       </c>
       <c r="I2">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="J2">
-        <v>-4.03</v>
+        <v>-4.46</v>
       </c>
       <c r="K2">
-        <v>-13.49</v>
+        <v>-17.9</v>
       </c>
       <c r="L2">
-        <v>-49.19</v>
+        <v>-52.42</v>
       </c>
       <c r="M2">
-        <v>18.1</v>
+        <v>16.56</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>22.57</v>
+        <v>22.62</v>
       </c>
       <c r="Q2">
-        <v>23.36</v>
+        <v>23.32</v>
       </c>
       <c r="R2">
-        <v>24.46</v>
+        <v>24.38</v>
       </c>
       <c r="S2">
-        <v>28.63</v>
+        <v>28.54</v>
       </c>
       <c r="T2">
-        <v>-19.36</v>
+        <v>-20.47</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -926,34 +925,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.2</v>
+        <v>42</v>
       </c>
       <c r="Z2">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2">
         <v>-0.52</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AC2">
-        <v>71.54000000000001</v>
+        <v>84.91</v>
       </c>
       <c r="AD2">
-        <v>41.72</v>
+        <v>66.56</v>
       </c>
       <c r="AE2">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AF2">
-        <v>12.47</v>
+        <v>-43.04</v>
       </c>
       <c r="AG2">
-        <v>24.76</v>
+        <v>24.75</v>
       </c>
       <c r="AH2">
-        <v>21.96</v>
+        <v>21.89</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -962,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>24.27</v>
+        <v>22.24</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1159,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>0.04</v>
+        <v>-4.03</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.03</v>
+        <v>-4.46</v>
       </c>
       <c r="E7" s="6">
-        <v>-4.07</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1177,13 +1176,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="D8" s="5">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.42</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1194,13 +1193,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-45.82</v>
+        <v>-49.19</v>
       </c>
       <c r="D9" s="5">
-        <v>-49.19</v>
+        <v>-52.42</v>
       </c>
       <c r="E9" s="6">
-        <v>-3.37</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1211,13 +1210,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-12.27</v>
+        <v>-13.49</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.49</v>
+        <v>-17.9</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.22</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1228,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.18</v>
+        <v>-53.9</v>
       </c>
       <c r="D11" s="5">
-        <v>-53.9</v>
+        <v>-54.68</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.72</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1245,13 +1244,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>23.45</v>
+        <v>23.09</v>
       </c>
       <c r="D12" s="5">
-        <v>23.09</v>
+        <v>22.7</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1262,13 +1261,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>48.35</v>
+        <v>45.2</v>
       </c>
       <c r="D13" s="5">
-        <v>45.2</v>
+        <v>42</v>
       </c>
       <c r="E13" s="6">
-        <v>-3.15</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1279,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>233.91</v>
+        <v>12.47</v>
       </c>
       <c r="D14" s="5">
-        <v>12.47</v>
+        <v>-43.04</v>
       </c>
       <c r="E14" s="6">
-        <v>-221.44</v>
+        <v>-55.51</v>
       </c>
     </row>
   </sheetData>
@@ -1350,16 +1349,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="9">
-        <v>45.2</v>
+        <v>42</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
       </c>
       <c r="F2" s="9">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="G2" s="9">
-        <v>-13.5</v>
+        <v>-17.9</v>
       </c>
       <c r="H2" s="9">
         <v>99</v>
@@ -1472,7 +1471,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12">
-        <v>0.181</v>
+        <v>0.1656</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,13 +234,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +269,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -726,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -862,34 +877,34 @@
         <v>22.7</v>
       </c>
       <c r="D2">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>50.09</v>
+        <v>48.91</v>
       </c>
       <c r="F2">
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.68</v>
+        <v>-53.59</v>
       </c>
       <c r="H2">
         <v>11.49</v>
       </c>
       <c r="I2">
-        <v>1.11</v>
+        <v>4.61</v>
       </c>
       <c r="J2">
-        <v>-4.46</v>
+        <v>-3.24</v>
       </c>
       <c r="K2">
         <v>-17.9</v>
       </c>
       <c r="L2">
-        <v>-52.42</v>
+        <v>-54.68</v>
       </c>
       <c r="M2">
-        <v>16.56</v>
+        <v>15.49</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -898,19 +913,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.62</v>
+        <v>22.82</v>
       </c>
       <c r="Q2">
-        <v>23.32</v>
+        <v>23.28</v>
       </c>
       <c r="R2">
-        <v>24.38</v>
+        <v>24.29</v>
       </c>
       <c r="S2">
-        <v>28.54</v>
+        <v>28.46</v>
       </c>
       <c r="T2">
-        <v>-20.47</v>
+        <v>-20.24</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -928,31 +943,31 @@
         <v>42</v>
       </c>
       <c r="Z2">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="AA2">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="AB2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>84.91</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AD2">
-        <v>66.56</v>
+        <v>77.45</v>
       </c>
       <c r="AE2">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AF2">
-        <v>-43.04</v>
+        <v>-51.33</v>
       </c>
       <c r="AG2">
-        <v>24.75</v>
+        <v>24.73</v>
       </c>
       <c r="AH2">
-        <v>21.89</v>
+        <v>21.82</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -961,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>22.24</v>
+        <v>20.76</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1159,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.03</v>
+        <v>-4.46</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.46</v>
+        <v>-3.24</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.43</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1176,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="D8" s="5">
-        <v>1.11</v>
+        <v>4.61</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.52</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1193,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-49.19</v>
+        <v>-52.42</v>
       </c>
       <c r="D9" s="5">
-        <v>-52.42</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-3.23</v>
+        <v>-54.68</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1207,16 +1222,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5">
-        <v>-13.49</v>
+        <v>-54.68</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.9</v>
+        <v>-53.59</v>
       </c>
       <c r="E10" s="6">
-        <v>-4.41</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1224,67 +1239,16 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.9</v>
+        <v>-43.04</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.68</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5">
-        <v>23.09</v>
-      </c>
-      <c r="D12" s="5">
-        <v>22.7</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5">
-        <v>45.2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>42</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
-        <v>12.47</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-43.04</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-55.51</v>
+        <v>-51.33</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-8.289999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1310,60 +1274,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>42</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-4.5</v>
-      </c>
-      <c r="G2" s="9">
+      <c r="F2" s="10">
+        <v>-3.2</v>
+      </c>
+      <c r="G2" s="10">
         <v>-17.9</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1465,13 +1429,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.1656</v>
+      <c r="A2" s="13">
+        <v>0.1549</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
   <si>
     <t>Symbol</t>
   </si>
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,7 +721,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,37 +873,37 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.7</v>
+        <v>22.71</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E2">
-        <v>48.91</v>
+        <v>48.83</v>
       </c>
       <c r="F2">
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-53.59</v>
+        <v>-53.49</v>
       </c>
       <c r="H2">
-        <v>11.49</v>
+        <v>11.54</v>
       </c>
       <c r="I2">
-        <v>4.61</v>
+        <v>2.53</v>
       </c>
       <c r="J2">
-        <v>-3.24</v>
+        <v>-3.61</v>
       </c>
       <c r="K2">
-        <v>-17.9</v>
+        <v>-17.84</v>
       </c>
       <c r="L2">
-        <v>-54.68</v>
+        <v>-53.57</v>
       </c>
       <c r="M2">
-        <v>15.49</v>
+        <v>15.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +912,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.82</v>
+        <v>22.93</v>
       </c>
       <c r="Q2">
-        <v>23.28</v>
+        <v>23.25</v>
       </c>
       <c r="R2">
-        <v>24.29</v>
+        <v>24.21</v>
       </c>
       <c r="S2">
-        <v>28.46</v>
+        <v>28.37</v>
       </c>
       <c r="T2">
-        <v>-20.24</v>
+        <v>-19.94</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42</v>
+        <v>42.12</v>
       </c>
       <c r="Z2">
-        <v>-0.49</v>
+        <v>-0.47</v>
       </c>
       <c r="AA2">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="AB2">
         <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>75.90000000000001</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="AD2">
-        <v>77.45</v>
+        <v>77.58</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-51.33</v>
+        <v>-46.93</v>
       </c>
       <c r="AG2">
-        <v>24.73</v>
+        <v>24.72</v>
       </c>
       <c r="AH2">
-        <v>21.82</v>
+        <v>21.77</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -976,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.76</v>
+        <v>19.47</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1174,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.46</v>
+        <v>-3.24</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.24</v>
+        <v>-3.61</v>
       </c>
       <c r="E7" s="6">
-        <v>1.22</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>1.11</v>
+        <v>4.61</v>
       </c>
       <c r="D8" s="5">
-        <v>4.61</v>
+        <v>2.53</v>
       </c>
       <c r="E8" s="6">
-        <v>3.5</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-52.42</v>
+        <v>-54.68</v>
       </c>
       <c r="D9" s="5">
-        <v>-54.68</v>
+        <v>-53.57</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.26</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1222,16 +1221,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-54.68</v>
+        <v>-17.9</v>
       </c>
       <c r="D10" s="5">
-        <v>-53.59</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.09</v>
+        <v>-17.84</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1239,16 +1238,67 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-53.59</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-53.49</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>22.7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>22.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5">
+        <v>42</v>
+      </c>
+      <c r="D13" s="5">
+        <v>42.12</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5">
-        <v>-43.04</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C14" s="5">
         <v>-51.33</v>
       </c>
-      <c r="E11" s="7">
-        <v>-8.289999999999999</v>
+      <c r="D14" s="5">
+        <v>-46.93</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
@@ -1313,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.2</v>
+        <v>-3.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-17.9</v>
+        <v>-17.8</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1435,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1549</v>
+        <v>0.1519</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -749,7 +749,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="7.7109375" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.71</v>
+        <v>22.45</v>
       </c>
       <c r="D2">
-        <v>0.04</v>
+        <v>-1.14</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-53.49</v>
+        <v>-54.02</v>
       </c>
       <c r="H2">
-        <v>11.54</v>
+        <v>10.27</v>
       </c>
       <c r="I2">
-        <v>2.53</v>
+        <v>-4.26</v>
       </c>
       <c r="J2">
-        <v>-3.61</v>
+        <v>-3.77</v>
       </c>
       <c r="K2">
-        <v>-17.84</v>
+        <v>-16.11</v>
       </c>
       <c r="L2">
-        <v>-53.57</v>
+        <v>-51.68</v>
       </c>
       <c r="M2">
-        <v>15.19</v>
+        <v>13.84</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>22.93</v>
+        <v>22.73</v>
       </c>
       <c r="Q2">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="R2">
-        <v>24.21</v>
+        <v>24.12</v>
       </c>
       <c r="S2">
-        <v>28.37</v>
+        <v>28.27</v>
       </c>
       <c r="T2">
-        <v>-19.94</v>
+        <v>-20.6</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.12</v>
+        <v>39.79</v>
       </c>
       <c r="Z2">
         <v>-0.47</v>
@@ -951,22 +951,22 @@
         <v>0.03</v>
       </c>
       <c r="AC2">
-        <v>71.93000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="AD2">
-        <v>77.58</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-46.93</v>
+        <v>-47.99</v>
       </c>
       <c r="AG2">
-        <v>24.72</v>
+        <v>24.71</v>
       </c>
       <c r="AH2">
-        <v>21.77</v>
+        <v>21.68</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>19.47</v>
+        <v>19.5</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.24</v>
+        <v>-3.61</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.61</v>
+        <v>-3.77</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.37</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>4.61</v>
+        <v>2.53</v>
       </c>
       <c r="D8" s="5">
-        <v>2.53</v>
+        <v>-4.26</v>
       </c>
       <c r="E8" s="6">
-        <v>-2.08</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-54.68</v>
+        <v>-53.57</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.57</v>
+        <v>-51.68</v>
       </c>
       <c r="E9" s="7">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-17.9</v>
+        <v>-17.84</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.84</v>
+        <v>-16.11</v>
       </c>
       <c r="E10" s="7">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.59</v>
+        <v>-53.49</v>
       </c>
       <c r="D11" s="5">
-        <v>-53.49</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.1</v>
+        <v>-54.02</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.7</v>
+        <v>22.71</v>
       </c>
       <c r="D12" s="5">
-        <v>22.71</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.01</v>
+        <v>22.45</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>42</v>
+        <v>42.12</v>
       </c>
       <c r="D13" s="5">
-        <v>42.12</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.12</v>
+        <v>39.79</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-51.33</v>
+        <v>-46.93</v>
       </c>
       <c r="D14" s="5">
-        <v>-46.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4.4</v>
+        <v>-47.99</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.06</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>42.1</v>
+        <v>39.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-17.8</v>
+        <v>-16.1</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1519</v>
+        <v>0.1384</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -749,7 +749,7 @@
     <col min="33" max="34" width="10.7109375" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" customWidth="1"/>
     <col min="36" max="36" width="14.7109375" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.45</v>
+        <v>22.09</v>
       </c>
       <c r="D2">
-        <v>-1.14</v>
+        <v>-1.6</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.02</v>
+        <v>-54.76</v>
       </c>
       <c r="H2">
-        <v>10.27</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
-        <v>-4.26</v>
+        <v>-4.33</v>
       </c>
       <c r="J2">
-        <v>-3.77</v>
+        <v>-5.64</v>
       </c>
       <c r="K2">
-        <v>-16.11</v>
+        <v>-18.09</v>
       </c>
       <c r="L2">
-        <v>-51.68</v>
+        <v>-50.61</v>
       </c>
       <c r="M2">
-        <v>13.84</v>
+        <v>14.15</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>22.73</v>
+        <v>22.53</v>
       </c>
       <c r="Q2">
-        <v>23.2</v>
+        <v>23.11</v>
       </c>
       <c r="R2">
-        <v>24.12</v>
+        <v>24.04</v>
       </c>
       <c r="S2">
-        <v>28.27</v>
+        <v>28.18</v>
       </c>
       <c r="T2">
-        <v>-20.6</v>
+        <v>-21.6</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +939,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.79</v>
+        <v>36.75</v>
       </c>
       <c r="Z2">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>69.12</v>
+        <v>61.93</v>
       </c>
       <c r="AD2">
-        <v>72.31999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-47.99</v>
+        <v>-45.03</v>
       </c>
       <c r="AG2">
-        <v>24.71</v>
+        <v>24.67</v>
       </c>
       <c r="AH2">
-        <v>21.68</v>
+        <v>21.55</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>21.67</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.61</v>
+        <v>-3.77</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.77</v>
+        <v>-5.64</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.16</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>2.53</v>
+        <v>-4.26</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.26</v>
+        <v>-4.33</v>
       </c>
       <c r="E8" s="6">
-        <v>-6.79</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.57</v>
+        <v>-51.68</v>
       </c>
       <c r="D9" s="5">
-        <v>-51.68</v>
+        <v>-50.61</v>
       </c>
       <c r="E9" s="7">
-        <v>1.89</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-17.84</v>
+        <v>-16.11</v>
       </c>
       <c r="D10" s="5">
-        <v>-16.11</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.73</v>
+        <v>-18.09</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-53.49</v>
+        <v>-54.02</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.02</v>
+        <v>-54.76</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.53</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.71</v>
+        <v>22.45</v>
       </c>
       <c r="D12" s="5">
-        <v>22.45</v>
+        <v>22.09</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>42.12</v>
+        <v>39.79</v>
       </c>
       <c r="D13" s="5">
-        <v>39.79</v>
+        <v>36.75</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.33</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-46.93</v>
+        <v>-47.99</v>
       </c>
       <c r="D14" s="5">
-        <v>-47.99</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.06</v>
+        <v>-45.03</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.96</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>39.8</v>
+        <v>36.8</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-16.1</v>
+        <v>-18.1</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1384</v>
+        <v>0.1415</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.09</v>
+        <v>22.26</v>
       </c>
       <c r="D2">
-        <v>-1.6</v>
+        <v>0.77</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.76</v>
+        <v>-54.41</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="I2">
-        <v>-4.33</v>
+        <v>-1.94</v>
       </c>
       <c r="J2">
-        <v>-5.64</v>
+        <v>-6.74</v>
       </c>
       <c r="K2">
-        <v>-18.09</v>
+        <v>-17.8</v>
       </c>
       <c r="L2">
-        <v>-50.61</v>
+        <v>-50.73</v>
       </c>
       <c r="M2">
-        <v>14.15</v>
+        <v>14.93</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>22.53</v>
+        <v>22.44</v>
       </c>
       <c r="Q2">
-        <v>23.11</v>
+        <v>23.02</v>
       </c>
       <c r="R2">
-        <v>24.04</v>
+        <v>23.96</v>
       </c>
       <c r="S2">
-        <v>28.18</v>
+        <v>28.08</v>
       </c>
       <c r="T2">
-        <v>-21.6</v>
+        <v>-20.73</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.75</v>
+        <v>39.11</v>
       </c>
       <c r="Z2">
         <v>-0.49</v>
@@ -951,22 +951,22 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>61.93</v>
+        <v>57.59</v>
       </c>
       <c r="AD2">
-        <v>67.66</v>
+        <v>62.88</v>
       </c>
       <c r="AE2">
         <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-45.03</v>
+        <v>-27.96</v>
       </c>
       <c r="AG2">
-        <v>24.67</v>
+        <v>24.55</v>
       </c>
       <c r="AH2">
-        <v>21.55</v>
+        <v>21.49</v>
       </c>
       <c r="AI2">
         <v>24.05</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.67</v>
+        <v>21.93</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.77</v>
+        <v>-5.64</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.64</v>
+        <v>-6.74</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.87</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.26</v>
+        <v>-4.33</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.33</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.07000000000000001</v>
+        <v>-1.94</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-51.68</v>
+        <v>-50.61</v>
       </c>
       <c r="D9" s="5">
-        <v>-50.61</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.07</v>
+        <v>-50.73</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-16.11</v>
+        <v>-18.09</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.09</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.98</v>
+        <v>-17.8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.02</v>
+        <v>-54.76</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.76</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.74</v>
+        <v>-54.41</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.45</v>
+        <v>22.09</v>
       </c>
       <c r="D12" s="5">
-        <v>22.09</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.36</v>
+        <v>22.26</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>39.79</v>
+        <v>36.75</v>
       </c>
       <c r="D13" s="5">
-        <v>36.75</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.04</v>
+        <v>39.11</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-47.99</v>
+        <v>-45.03</v>
       </c>
       <c r="D14" s="5">
-        <v>-45.03</v>
+        <v>-27.96</v>
       </c>
       <c r="E14" s="7">
-        <v>2.96</v>
+        <v>17.07</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>36.8</v>
+        <v>39.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.6</v>
+        <v>-6.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-18.1</v>
+        <v>-17.8</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1415</v>
+        <v>0.1493</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.26</v>
+        <v>22.05</v>
       </c>
       <c r="D2">
-        <v>0.77</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.41</v>
+        <v>-54.84</v>
       </c>
       <c r="H2">
-        <v>9.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
-        <v>-1.94</v>
+        <v>-2.86</v>
       </c>
       <c r="J2">
-        <v>-6.74</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K2">
-        <v>-17.8</v>
+        <v>-19.5</v>
       </c>
       <c r="L2">
-        <v>-50.73</v>
+        <v>-49.8</v>
       </c>
       <c r="M2">
-        <v>14.93</v>
+        <v>13.61</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>22.44</v>
+        <v>22.31</v>
       </c>
       <c r="Q2">
-        <v>23.02</v>
+        <v>22.91</v>
       </c>
       <c r="R2">
-        <v>23.96</v>
+        <v>23.88</v>
       </c>
       <c r="S2">
-        <v>28.08</v>
+        <v>27.98</v>
       </c>
       <c r="T2">
-        <v>-20.73</v>
+        <v>-21.21</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.11</v>
+        <v>37.26</v>
       </c>
       <c r="Z2">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC2">
-        <v>57.59</v>
+        <v>53.94</v>
       </c>
       <c r="AD2">
-        <v>62.88</v>
+        <v>57.82</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-27.96</v>
+        <v>-49.4</v>
       </c>
       <c r="AG2">
-        <v>24.55</v>
+        <v>24.4</v>
       </c>
       <c r="AH2">
-        <v>21.49</v>
+        <v>21.42</v>
       </c>
       <c r="AI2">
-        <v>24.05</v>
+        <v>23.98</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.93</v>
+        <v>23.15</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.64</v>
+        <v>-6.74</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.74</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.1</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.33</v>
+        <v>-1.94</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.39</v>
+        <v>-2.86</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-50.61</v>
+        <v>-50.73</v>
       </c>
       <c r="D9" s="5">
-        <v>-50.73</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.12</v>
+        <v>-49.8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.09</v>
+        <v>-17.8</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.8</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.29</v>
+        <v>-19.5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.76</v>
+        <v>-54.41</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.41</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.35</v>
+        <v>-54.84</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.09</v>
+        <v>22.26</v>
       </c>
       <c r="D12" s="5">
-        <v>22.26</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.17</v>
+        <v>22.05</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>36.75</v>
+        <v>39.11</v>
       </c>
       <c r="D13" s="5">
-        <v>39.11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.36</v>
+        <v>37.26</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-45.03</v>
+        <v>-27.96</v>
       </c>
       <c r="D14" s="5">
-        <v>-27.96</v>
-      </c>
-      <c r="E14" s="7">
-        <v>17.07</v>
+        <v>-49.4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-21.44</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.7</v>
+        <v>-8.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-17.8</v>
+        <v>-19.5</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1493</v>
+        <v>0.1361</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -873,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
       <c r="D2">
-        <v>-0.9399999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,46 +885,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.84</v>
+        <v>-54.88</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
-        <v>-2.86</v>
+        <v>-2.99</v>
       </c>
       <c r="J2">
-        <v>-8.390000000000001</v>
+        <v>-8.85</v>
       </c>
       <c r="K2">
-        <v>-19.5</v>
+        <v>-22.95</v>
       </c>
       <c r="L2">
-        <v>-49.8</v>
+        <v>-49.98</v>
       </c>
       <c r="M2">
-        <v>13.61</v>
+        <v>12.55</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>22.31</v>
+        <v>22.18</v>
       </c>
       <c r="Q2">
-        <v>22.91</v>
+        <v>22.8</v>
       </c>
       <c r="R2">
-        <v>23.88</v>
+        <v>23.82</v>
       </c>
       <c r="S2">
-        <v>27.98</v>
+        <v>27.89</v>
       </c>
       <c r="T2">
-        <v>-21.21</v>
+        <v>-21.01</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.26</v>
+        <v>37.08</v>
       </c>
       <c r="Z2">
         <v>-0.51</v>
@@ -951,22 +951,22 @@
         <v>-0.01</v>
       </c>
       <c r="AC2">
-        <v>53.94</v>
+        <v>54.42</v>
       </c>
       <c r="AD2">
-        <v>57.82</v>
+        <v>55.32</v>
       </c>
       <c r="AE2">
         <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>-49.4</v>
+        <v>-43.56</v>
       </c>
       <c r="AG2">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="AH2">
-        <v>21.42</v>
+        <v>21.4</v>
       </c>
       <c r="AI2">
         <v>23.98</v>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>23.15</v>
+        <v>21.58</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.74</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.390000000000001</v>
+        <v>-8.85</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.65</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.94</v>
+        <v>-2.86</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.86</v>
+        <v>-2.99</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.92</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-50.73</v>
+        <v>-49.8</v>
       </c>
       <c r="D9" s="5">
-        <v>-49.8</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.93</v>
+        <v>-49.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-17.8</v>
+        <v>-19.5</v>
       </c>
       <c r="D10" s="5">
-        <v>-19.5</v>
+        <v>-22.95</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.7</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.41</v>
+        <v>-54.84</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.84</v>
+        <v>-54.88</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.43</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.26</v>
+        <v>22.05</v>
       </c>
       <c r="D12" s="5">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.21</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>39.11</v>
+        <v>37.26</v>
       </c>
       <c r="D13" s="5">
-        <v>37.26</v>
+        <v>37.08</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.85</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-27.96</v>
+        <v>-49.4</v>
       </c>
       <c r="D14" s="5">
-        <v>-49.4</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-21.44</v>
+        <v>-43.56</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5.84</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="G2" s="10">
-        <v>-19.5</v>
+        <v>-23</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1361</v>
+        <v>0.1255</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -740,7 +740,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.03</v>
+        <v>22.08</v>
       </c>
       <c r="D2">
-        <v>-0.09</v>
+        <v>0.23</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +886,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.88</v>
+        <v>-54.78</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I2">
-        <v>-2.99</v>
+        <v>-1.65</v>
       </c>
       <c r="J2">
-        <v>-8.85</v>
+        <v>-8.91</v>
       </c>
       <c r="K2">
-        <v>-22.95</v>
+        <v>-18.97</v>
       </c>
       <c r="L2">
-        <v>-49.98</v>
+        <v>-52.25</v>
       </c>
       <c r="M2">
-        <v>12.55</v>
+        <v>12.52</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +913,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.18</v>
+        <v>22.1</v>
       </c>
       <c r="Q2">
-        <v>22.8</v>
+        <v>22.69</v>
       </c>
       <c r="R2">
-        <v>23.82</v>
+        <v>23.76</v>
       </c>
       <c r="S2">
-        <v>27.89</v>
+        <v>27.8</v>
       </c>
       <c r="T2">
-        <v>-21.01</v>
+        <v>-20.58</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,34 +940,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.08</v>
+        <v>37.89</v>
       </c>
       <c r="Z2">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC2">
-        <v>54.42</v>
+        <v>52.65</v>
       </c>
       <c r="AD2">
-        <v>55.32</v>
+        <v>53.67</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="AF2">
-        <v>-43.56</v>
+        <v>-29.63</v>
       </c>
       <c r="AG2">
-        <v>24.2</v>
+        <v>23.92</v>
       </c>
       <c r="AH2">
-        <v>21.4</v>
+        <v>21.46</v>
       </c>
       <c r="AI2">
         <v>23.98</v>
@@ -975,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.58</v>
+        <v>20.22</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.390000000000001</v>
+        <v>-8.85</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.85</v>
+        <v>-8.91</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.46</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.86</v>
+        <v>-2.99</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.13</v>
+        <v>-1.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-49.8</v>
+        <v>-49.98</v>
       </c>
       <c r="D9" s="5">
-        <v>-49.98</v>
+        <v>-52.25</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.18</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-19.5</v>
+        <v>-22.95</v>
       </c>
       <c r="D10" s="5">
-        <v>-22.95</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-3.45</v>
+        <v>-18.97</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.84</v>
+        <v>-54.88</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.88</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.04</v>
+        <v>-54.78</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.05</v>
+        <v>22.03</v>
       </c>
       <c r="D12" s="5">
-        <v>22.03</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.02</v>
+        <v>22.08</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.26</v>
+        <v>37.08</v>
       </c>
       <c r="D13" s="5">
-        <v>37.08</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.18</v>
+        <v>37.89</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-49.4</v>
+        <v>-43.56</v>
       </c>
       <c r="D14" s="5">
-        <v>-43.56</v>
+        <v>-29.63</v>
       </c>
       <c r="E14" s="7">
-        <v>5.84</v>
+        <v>13.93</v>
       </c>
     </row>
   </sheetData>
@@ -1363,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>37.1</v>
+        <v>37.9</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-23</v>
+        <v>-19</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1485,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1255</v>
+        <v>0.1252</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -874,10 +874,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.08</v>
+        <v>21.94</v>
       </c>
       <c r="D2">
-        <v>0.23</v>
+        <v>-0.63</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -886,25 +886,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.78</v>
+        <v>-55.07</v>
       </c>
       <c r="H2">
-        <v>8.449999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="I2">
-        <v>-1.65</v>
+        <v>-0.68</v>
       </c>
       <c r="J2">
-        <v>-8.91</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="K2">
-        <v>-18.97</v>
+        <v>-21.02</v>
       </c>
       <c r="L2">
-        <v>-52.25</v>
+        <v>-54.05</v>
       </c>
       <c r="M2">
-        <v>12.52</v>
+        <v>12.73</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +913,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.1</v>
+        <v>22.07</v>
       </c>
       <c r="Q2">
-        <v>22.69</v>
+        <v>22.59</v>
       </c>
       <c r="R2">
-        <v>23.76</v>
+        <v>23.72</v>
       </c>
       <c r="S2">
-        <v>27.8</v>
+        <v>27.71</v>
       </c>
       <c r="T2">
-        <v>-20.58</v>
+        <v>-20.82</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.89</v>
+        <v>36.47</v>
       </c>
       <c r="Z2">
         <v>-0.5</v>
@@ -952,22 +952,22 @@
         <v>-0</v>
       </c>
       <c r="AC2">
-        <v>52.65</v>
+        <v>51.52</v>
       </c>
       <c r="AD2">
-        <v>53.67</v>
+        <v>52.86</v>
       </c>
       <c r="AE2">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AF2">
-        <v>-29.63</v>
+        <v>4.3</v>
       </c>
       <c r="AG2">
-        <v>23.92</v>
+        <v>23.71</v>
       </c>
       <c r="AH2">
-        <v>21.46</v>
+        <v>21.47</v>
       </c>
       <c r="AI2">
         <v>23.98</v>
@@ -976,7 +976,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.22</v>
+        <v>20.91</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.85</v>
+        <v>-8.91</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.91</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.06</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1191,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.99</v>
+        <v>-1.65</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.65</v>
+        <v>-0.68</v>
       </c>
       <c r="E8" s="7">
-        <v>1.34</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1208,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-49.98</v>
+        <v>-52.25</v>
       </c>
       <c r="D9" s="5">
-        <v>-52.25</v>
+        <v>-54.05</v>
       </c>
       <c r="E9" s="6">
-        <v>-2.27</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-22.95</v>
+        <v>-18.97</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.97</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.98</v>
+        <v>-21.02</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.88</v>
+        <v>-54.78</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.78</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.1</v>
+        <v>-55.07</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.03</v>
+        <v>22.08</v>
       </c>
       <c r="D12" s="5">
-        <v>22.08</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.05</v>
+        <v>21.94</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1276,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.08</v>
+        <v>37.89</v>
       </c>
       <c r="D13" s="5">
-        <v>37.89</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.8100000000000001</v>
+        <v>36.47</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1293,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-43.56</v>
+        <v>-29.63</v>
       </c>
       <c r="D14" s="5">
-        <v>-29.63</v>
+        <v>4.3</v>
       </c>
       <c r="E14" s="7">
-        <v>13.93</v>
+        <v>33.93</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>37.9</v>
+        <v>36.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1252</v>
+        <v>0.1273</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -234,14 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -274,13 +274,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -874,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.94</v>
+        <v>21.71</v>
       </c>
       <c r="D2">
-        <v>-0.63</v>
+        <v>-1.05</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -886,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.07</v>
+        <v>-55.54</v>
       </c>
       <c r="H2">
-        <v>7.76</v>
+        <v>6.63</v>
       </c>
       <c r="I2">
-        <v>-0.68</v>
+        <v>-2.47</v>
       </c>
       <c r="J2">
-        <v>-9.859999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="K2">
-        <v>-21.02</v>
+        <v>-18.6</v>
       </c>
       <c r="L2">
-        <v>-54.05</v>
+        <v>-53.24</v>
       </c>
       <c r="M2">
-        <v>12.73</v>
+        <v>11.41</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -913,19 +912,19 @@
         <v>3</v>
       </c>
       <c r="P2">
-        <v>22.07</v>
+        <v>21.96</v>
       </c>
       <c r="Q2">
-        <v>22.59</v>
+        <v>22.49</v>
       </c>
       <c r="R2">
-        <v>23.72</v>
+        <v>23.66</v>
       </c>
       <c r="S2">
-        <v>27.71</v>
+        <v>27.62</v>
       </c>
       <c r="T2">
-        <v>-20.82</v>
+        <v>-21.4</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -940,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.47</v>
+        <v>34.21</v>
       </c>
       <c r="Z2">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC2">
-        <v>51.52</v>
+        <v>37.9</v>
       </c>
       <c r="AD2">
-        <v>52.86</v>
+        <v>47.36</v>
       </c>
       <c r="AE2">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="AF2">
-        <v>4.3</v>
+        <v>-14.53</v>
       </c>
       <c r="AG2">
-        <v>23.71</v>
+        <v>23.57</v>
       </c>
       <c r="AH2">
-        <v>21.47</v>
+        <v>21.42</v>
       </c>
       <c r="AI2">
-        <v>23.98</v>
+        <v>23.69</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.91</v>
+        <v>22.36</v>
       </c>
     </row>
   </sheetData>
@@ -1174,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.91</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.859999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.95</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1191,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.65</v>
+        <v>-0.68</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.68</v>
+        <v>-2.47</v>
       </c>
       <c r="E8" s="7">
-        <v>0.97</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1208,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-52.25</v>
+        <v>-54.05</v>
       </c>
       <c r="D9" s="5">
-        <v>-54.05</v>
+        <v>-53.24</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.8</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1225,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.97</v>
+        <v>-21.02</v>
       </c>
       <c r="D10" s="5">
-        <v>-21.02</v>
+        <v>-18.6</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.05</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1242,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.78</v>
+        <v>-55.07</v>
       </c>
       <c r="D11" s="5">
-        <v>-55.07</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.29</v>
+        <v>-55.54</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1259,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.08</v>
+        <v>21.94</v>
       </c>
       <c r="D12" s="5">
-        <v>21.94</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.14</v>
+        <v>21.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1276,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>37.89</v>
+        <v>36.47</v>
       </c>
       <c r="D13" s="5">
-        <v>36.47</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.42</v>
+        <v>34.21</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1293,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-29.63</v>
+        <v>4.3</v>
       </c>
       <c r="D14" s="5">
-        <v>4.3</v>
+        <v>-14.53</v>
       </c>
       <c r="E14" s="7">
-        <v>33.93</v>
+        <v>-18.83</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1363,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="10">
-        <v>36.5</v>
+        <v>34.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.9</v>
+        <v>-9.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-21</v>
+        <v>-18.6</v>
       </c>
       <c r="H2" s="10">
         <v>99</v>
@@ -1486,7 +1485,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="13">
-        <v>0.1273</v>
+        <v>0.1141</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,15 +239,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,12 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +347,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -740,7 +726,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,10 +860,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.71</v>
+        <v>22.01</v>
       </c>
       <c r="D2">
-        <v>-1.05</v>
+        <v>1.38</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,46 +872,46 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.54</v>
+        <v>-54.93</v>
       </c>
       <c r="H2">
-        <v>6.63</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
-        <v>-2.47</v>
+        <v>-0.18</v>
       </c>
       <c r="J2">
-        <v>-9.390000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="K2">
-        <v>-18.6</v>
+        <v>-14.42</v>
       </c>
       <c r="L2">
-        <v>-53.24</v>
+        <v>-53.09</v>
       </c>
       <c r="M2">
-        <v>11.41</v>
+        <v>10.68</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>21.96</v>
+        <v>21.95</v>
       </c>
       <c r="Q2">
-        <v>22.49</v>
+        <v>22.42</v>
       </c>
       <c r="R2">
-        <v>23.66</v>
+        <v>23.56</v>
       </c>
       <c r="S2">
-        <v>27.62</v>
+        <v>27.54</v>
       </c>
       <c r="T2">
-        <v>-21.4</v>
+        <v>-20.07</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,31 +926,31 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.21</v>
+        <v>39.48</v>
       </c>
       <c r="Z2">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>37.9</v>
+        <v>32.08</v>
       </c>
       <c r="AD2">
-        <v>47.36</v>
+        <v>40.5</v>
       </c>
       <c r="AE2">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-14.53</v>
+        <v>316.83</v>
       </c>
       <c r="AG2">
-        <v>23.57</v>
+        <v>23.43</v>
       </c>
       <c r="AH2">
         <v>21.42</v>
@@ -975,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>22.36</v>
+        <v>21.26</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1160,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.859999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>-9.390000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="E7" s="6">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.68</v>
+        <v>-2.47</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.47</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.79</v>
+        <v>-0.18</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1194,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-54.05</v>
+        <v>-53.24</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.24</v>
+        <v>-53.09</v>
       </c>
       <c r="E9" s="6">
-        <v>0.8100000000000001</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1211,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-21.02</v>
+        <v>-18.6</v>
       </c>
       <c r="D10" s="5">
-        <v>-18.6</v>
+        <v>-14.42</v>
       </c>
       <c r="E10" s="6">
-        <v>2.42</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1228,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-55.07</v>
+        <v>-55.54</v>
       </c>
       <c r="D11" s="5">
-        <v>-55.54</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.47</v>
+        <v>-54.93</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1245,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.94</v>
+        <v>21.71</v>
       </c>
       <c r="D12" s="5">
-        <v>21.71</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.23</v>
+        <v>22.01</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1262,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>36.47</v>
+        <v>34.21</v>
       </c>
       <c r="D13" s="5">
-        <v>34.21</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.26</v>
+        <v>39.48</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1279,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>4.3</v>
+        <v>-14.53</v>
       </c>
       <c r="D14" s="5">
-        <v>-14.53</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-18.83</v>
+        <v>316.83</v>
+      </c>
+      <c r="E14" s="6">
+        <v>331.36</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1311,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>34.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>39.5</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-18.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-6.8</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-14.4</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.1141</v>
+      <c r="A2" s="12">
+        <v>0.1068</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +239,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +275,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,10 +360,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -726,8 +740,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -860,10 +873,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>22.01</v>
+        <v>21.84</v>
       </c>
       <c r="D2">
-        <v>1.38</v>
+        <v>-0.77</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -872,25 +885,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-54.93</v>
+        <v>-55.27</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.27</v>
       </c>
       <c r="I2">
-        <v>-0.18</v>
+        <v>-0.86</v>
       </c>
       <c r="J2">
-        <v>-6.82</v>
+        <v>-6.59</v>
       </c>
       <c r="K2">
-        <v>-14.42</v>
+        <v>-17.93</v>
       </c>
       <c r="L2">
-        <v>-53.09</v>
+        <v>-52.7</v>
       </c>
       <c r="M2">
-        <v>10.68</v>
+        <v>9.48</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -899,19 +912,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21.95</v>
+        <v>21.92</v>
       </c>
       <c r="Q2">
-        <v>22.42</v>
+        <v>22.36</v>
       </c>
       <c r="R2">
-        <v>23.56</v>
+        <v>23.46</v>
       </c>
       <c r="S2">
-        <v>27.54</v>
+        <v>27.46</v>
       </c>
       <c r="T2">
-        <v>-20.07</v>
+        <v>-20.47</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -926,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.48</v>
+        <v>37.64</v>
       </c>
       <c r="Z2">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
@@ -938,22 +951,22 @@
         <v>0.01</v>
       </c>
       <c r="AC2">
+        <v>26.27</v>
+      </c>
+      <c r="AD2">
         <v>32.08</v>
       </c>
-      <c r="AD2">
-        <v>40.5</v>
-      </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="AF2">
-        <v>316.83</v>
+        <v>-25.27</v>
       </c>
       <c r="AG2">
-        <v>23.43</v>
+        <v>23.32</v>
       </c>
       <c r="AH2">
-        <v>21.42</v>
+        <v>21.39</v>
       </c>
       <c r="AI2">
         <v>23.69</v>
@@ -962,7 +975,7 @@
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>21.26</v>
+        <v>20.31</v>
       </c>
     </row>
   </sheetData>
@@ -1160,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.390000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.82</v>
+        <v>-6.59</v>
       </c>
       <c r="E7" s="6">
-        <v>2.57</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1177,13 +1190,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.47</v>
+        <v>-0.18</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.18</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2.29</v>
+        <v>-0.86</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1194,13 +1207,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.24</v>
+        <v>-53.09</v>
       </c>
       <c r="D9" s="5">
-        <v>-53.09</v>
+        <v>-52.7</v>
       </c>
       <c r="E9" s="6">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1211,13 +1224,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-18.6</v>
+        <v>-14.42</v>
       </c>
       <c r="D10" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="E10" s="6">
-        <v>4.18</v>
+        <v>-17.93</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1228,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-55.54</v>
+        <v>-54.93</v>
       </c>
       <c r="D11" s="5">
-        <v>-54.93</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.61</v>
+        <v>-55.27</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1245,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>21.71</v>
+        <v>22.01</v>
       </c>
       <c r="D12" s="5">
-        <v>22.01</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.3</v>
+        <v>21.84</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1262,13 +1275,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>34.21</v>
+        <v>39.48</v>
       </c>
       <c r="D13" s="5">
-        <v>39.48</v>
-      </c>
-      <c r="E13" s="6">
-        <v>5.27</v>
+        <v>37.64</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1279,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.53</v>
+        <v>316.83</v>
       </c>
       <c r="D14" s="5">
-        <v>316.83</v>
-      </c>
-      <c r="E14" s="6">
-        <v>331.36</v>
+        <v>-25.27</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-342.1</v>
       </c>
     </row>
   </sheetData>
@@ -1311,60 +1324,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>49.6</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
-        <v>39.5</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="D2" s="10">
+        <v>37.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
-        <v>-6.8</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-14.4</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="F2" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-17.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>99</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1466,13 +1479,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="12">
-        <v>0.1068</v>
+      <c r="A2" s="13">
+        <v>0.09480000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/ANIL_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -200,7 +200,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,20 +234,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -360,11 +347,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -740,7 +726,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -873,10 +860,10 @@
         <v>38</v>
       </c>
       <c r="C2">
-        <v>21.84</v>
+        <v>21.58</v>
       </c>
       <c r="D2">
-        <v>-0.77</v>
+        <v>-1.19</v>
       </c>
       <c r="E2">
         <v>48.83</v>
@@ -885,25 +872,25 @@
         <v>20.36</v>
       </c>
       <c r="G2">
-        <v>-55.27</v>
+        <v>-55.81</v>
       </c>
       <c r="H2">
-        <v>7.27</v>
+        <v>5.99</v>
       </c>
       <c r="I2">
-        <v>-0.86</v>
+        <v>-2.26</v>
       </c>
       <c r="J2">
-        <v>-6.59</v>
+        <v>-7.06</v>
       </c>
       <c r="K2">
-        <v>-17.93</v>
+        <v>-18.99</v>
       </c>
       <c r="L2">
-        <v>-52.7</v>
+        <v>-53.72</v>
       </c>
       <c r="M2">
-        <v>9.48</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -912,19 +899,19 @@
         <v>4</v>
       </c>
       <c r="P2">
-        <v>21.92</v>
+        <v>21.82</v>
       </c>
       <c r="Q2">
-        <v>22.36</v>
+        <v>22.29</v>
       </c>
       <c r="R2">
-        <v>23.46</v>
+        <v>23.38</v>
       </c>
       <c r="S2">
-        <v>27.46</v>
+        <v>27.38</v>
       </c>
       <c r="T2">
-        <v>-20.47</v>
+        <v>-21.19</v>
       </c>
       <c r="U2" t="s">
         <v>39</v>
@@ -939,43 +926,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.64</v>
+        <v>34.96</v>
       </c>
       <c r="Z2">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2">
         <v>-0.5</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>26.27</v>
+        <v>25.96</v>
       </c>
       <c r="AD2">
-        <v>32.08</v>
+        <v>28.1</v>
       </c>
       <c r="AE2">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="AF2">
-        <v>-25.27</v>
+        <v>-26.67</v>
       </c>
       <c r="AG2">
-        <v>23.32</v>
+        <v>23.26</v>
       </c>
       <c r="AH2">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="AI2">
-        <v>23.69</v>
+        <v>23.53</v>
       </c>
       <c r="AJ2" t="s">
         <v>40</v>
       </c>
       <c r="AK2">
-        <v>20.31</v>
+        <v>18.13</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1160,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.82</v>
+        <v>-6.59</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.59</v>
+        <v>-7.06</v>
       </c>
       <c r="E7" s="6">
-        <v>0.23</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1190,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.18</v>
+        <v>-0.86</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.86</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.68</v>
+        <v>-2.26</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1207,13 +1194,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>-53.09</v>
+        <v>-52.7</v>
       </c>
       <c r="D9" s="5">
-        <v>-52.7</v>
+        <v>-53.72</v>
       </c>
       <c r="E9" s="6">
-        <v>0.39</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1224,13 +1211,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.42</v>
+        <v>-17.93</v>
       </c>
       <c r="D10" s="5">
-        <v>-17.93</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.51</v>
+        <v>-18.99</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1241,13 +1228,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="5">
-        <v>-54.93</v>
+        <v>-55.27</v>
       </c>
       <c r="D11" s="5">
-        <v>-55.27</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.34</v>
+        <v>-55.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1258,13 +1245,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>22.01</v>
+        <v>21.84</v>
       </c>
       <c r="D12" s="5">
-        <v>21.84</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.17</v>
+        <v>21.58</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1275,13 +1262,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="5">
-        <v>39.48</v>
+        <v>37.64</v>
       </c>
       <c r="D13" s="5">
-        <v>37.64</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.84</v>
+        <v>34.96</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1292,13 +1279,13 @@
         <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>316.83</v>
+        <v>-25.27</v>
       </c>
       <c r="D14" s="5">
-        <v>-25.27</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-342.1</v>
+        <v>-26.67</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1324,60 +1311,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>49.6</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
-      <c r="D2" s="10">
-        <v>37.6</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="9">
+        <v>35</v>
+      </c>
+      <c r="E2" s="9">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-17.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="9">
+        <v>-7.1</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-19</v>
+      </c>
+      <c r="H2" s="9">
         <v>99</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1479,13 +1466,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="13">
-        <v>0.09480000000000001</v>
+      <c r="A2" s="12">
+        <v>0.09210000000000002</v>
       </c>
     </row>
   </sheetData>
